--- a/结果/问题一_18架次方案_修复版.xlsx
+++ b/结果/问题一_18架次方案_修复版.xlsx
@@ -672,33 +672,33 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>S002-HYG-01,S002-FOD-01,S002-FOD-02,S002-WAT-01,S002-WAT-02,S002-MED-01</t>
+          <t>S002-FOD-02,S002-WAT-01,S002-WAT-02,S002-MED-01</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="G4" t="n">
-        <v>0.157</v>
+        <v>0.094</v>
       </c>
       <c r="H4" t="n">
-        <v>4.961223970153424</v>
+        <v>4.597693179653722</v>
       </c>
       <c r="I4" t="n">
         <v>20.55455664662418</v>
       </c>
       <c r="J4" t="n">
-        <v>24.80077832331209</v>
+        <v>22.60077832331209</v>
       </c>
       <c r="K4" t="n">
-        <v>14.6</v>
+        <v>12.4</v>
       </c>
       <c r="L4" t="n">
-        <v>35.15455664662418</v>
+        <v>32.95455664662418</v>
       </c>
       <c r="M4" t="n">
         <v>257.9912772349467</v>
@@ -710,13 +710,13 @@
         <v>6.4</v>
       </c>
       <c r="P4" t="n">
-        <v>1.438776029846577</v>
+        <v>1.802306820346279</v>
       </c>
       <c r="Q4" t="n">
-        <v>16.725</v>
+        <v>19.175</v>
       </c>
       <c r="R4" t="n">
-        <v>1.854463503381801</v>
+        <v>4.3044635033818</v>
       </c>
       <c r="S4" t="b">
         <v>1</v>
@@ -733,37 +733,37 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>S002-WAT-03,S002-WAT-04</t>
+          <t>S002-WAT-03,S002-WAT-04,S002-HYG-01,S002-FOD-01</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>0.054</v>
+        <v>0.117</v>
       </c>
       <c r="H5" t="n">
-        <v>2.376571336180863</v>
+        <v>4.667552074381116</v>
       </c>
       <c r="I5" t="n">
-        <v>19.80793843976337</v>
+        <v>20.55455664662418</v>
       </c>
       <c r="J5" t="n">
-        <v>19.35296921988168</v>
+        <v>22.60077832331209</v>
       </c>
       <c r="K5" t="n">
-        <v>9.5</v>
+        <v>12.4</v>
       </c>
       <c r="L5" t="n">
-        <v>29.30793843976337</v>
+        <v>32.95455664662418</v>
       </c>
       <c r="M5" t="n">
         <v>257.9912772349467</v>
@@ -772,16 +772,16 @@
         <v>307.9912772349467</v>
       </c>
       <c r="O5" t="n">
-        <v>3.2</v>
+        <v>6.4</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8234286638191368</v>
+        <v>1.732447925618884</v>
       </c>
       <c r="Q5" t="n">
-        <v>16.8</v>
+        <v>18.65</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9294635033818</v>
+        <v>3.779463503381798</v>
       </c>
       <c r="S5" t="b">
         <v>1</v>
@@ -802,33 +802,33 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S003-WAT-01,S003-WAT-02,S003-WAT-03,S003-WAT-04,S003-FOD-01</t>
+          <t>S003-WAT-03,S003-WAT-04,S003-MED-01,S003-HYG-01</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="G6" t="n">
-        <v>0.136</v>
+        <v>0.101</v>
       </c>
       <c r="H6" t="n">
-        <v>5.615775464840262</v>
+        <v>4.855922808999017</v>
       </c>
       <c r="I6" t="n">
         <v>25.84784125293697</v>
       </c>
       <c r="J6" t="n">
-        <v>26.24825395980182</v>
+        <v>25.14825395980182</v>
       </c>
       <c r="K6" t="n">
-        <v>13.5</v>
+        <v>12.4</v>
       </c>
       <c r="L6" t="n">
-        <v>39.34784125293697</v>
+        <v>38.24784125293696</v>
       </c>
       <c r="M6" t="n">
         <v>506.8380016939101</v>
@@ -840,13 +840,13 @@
         <v>6.4</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7842245351597388</v>
+        <v>1.544077191000984</v>
       </c>
       <c r="Q6" t="n">
-        <v>14.8</v>
+        <v>19.525</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2778689180923042</v>
+        <v>5.002868918092302</v>
       </c>
       <c r="S6" t="b">
         <v>1</v>
@@ -867,33 +867,33 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>S003-FOD-02,S003-HYG-01,S003-MED-01</t>
+          <t>S003-FOD-01,S003-FOD-02,S003-WAT-01,S003-WAT-02</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="G7" t="n">
-        <v>0.07500000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="H7" t="n">
-        <v>4.494131863361813</v>
+        <v>5.015244272559334</v>
       </c>
       <c r="I7" t="n">
         <v>25.84784125293697</v>
       </c>
       <c r="J7" t="n">
-        <v>24.04825395980182</v>
+        <v>25.14825395980182</v>
       </c>
       <c r="K7" t="n">
-        <v>11.3</v>
+        <v>12.4</v>
       </c>
       <c r="L7" t="n">
-        <v>37.14784125293696</v>
+        <v>38.24784125293696</v>
       </c>
       <c r="M7" t="n">
         <v>506.8380016939101</v>
@@ -905,13 +905,13 @@
         <v>6.4</v>
       </c>
       <c r="P7" t="n">
-        <v>1.905868136638187</v>
+        <v>1.384755727440666</v>
       </c>
       <c r="Q7" t="n">
-        <v>23.025</v>
+        <v>18.3</v>
       </c>
       <c r="R7" t="n">
-        <v>8.502868918092302</v>
+        <v>3.777868918092304</v>
       </c>
       <c r="S7" t="b">
         <v>1</v>
@@ -2036,7 +2036,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S002-HYG-01</t>
+          <t>S002-FOD-02</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2056,7 +2056,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S002-FOD-01</t>
+          <t>S002-WAT-01</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2076,7 +2076,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S002-FOD-02</t>
+          <t>S002-WAT-02</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2096,7 +2096,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S002-WAT-01</t>
+          <t>S002-MED-01</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2116,11 +2116,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S002-WAT-02</t>
+          <t>S002-WAT-03</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2136,11 +2136,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S002-MED-01</t>
+          <t>S002-WAT-04</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S002-WAT-03</t>
+          <t>S002-HYG-01</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S002-WAT-04</t>
+          <t>S002-FOD-01</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -2189,14 +2189,14 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S003-WAT-01</t>
+          <t>S003-WAT-03</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2216,7 +2216,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S003-WAT-02</t>
+          <t>S003-WAT-04</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2236,7 +2236,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S003-WAT-03</t>
+          <t>S003-MED-01</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2256,7 +2256,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S003-WAT-04</t>
+          <t>S003-HYG-01</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S003-HYG-01</t>
+          <t>S003-WAT-01</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -2336,7 +2336,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S003-MED-01</t>
+          <t>S003-WAT-02</t>
         </is>
       </c>
       <c r="B32" t="n">
